--- a/timesheet_data.xlsx
+++ b/timesheet_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dinop\Documents\DTS\auto-dts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED17E605-6DDE-4A38-A72A-EF0B82F10A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3FDF59-6A62-41EE-82F5-EDD130F1D691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1628D00C-3FD5-4A0E-AF48-DB394FB0EAAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1628D00C-3FD5-4A0E-AF48-DB394FB0EAAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Timesheet" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="181">
   <si>
     <t>Date</t>
   </si>
@@ -57,17 +57,539 @@
     <t>OT Hours</t>
   </si>
   <si>
-    <t>DIRECT_ACTIVITIES = { "Coding &gt; Test Framework Code Creation": 42394, "Coding &gt; Test Framework Code Review": 42395, "Coding &gt; [Tool] Source Code Creation": 42396, "Coding &gt; [Tool] Source Code Modification": 42398, "Coding &gt; [Tool] Source Code Review": 42397, "Environment Configuration and Management &gt; Environment Setup": 42391, "Environment Configuration and Management &gt; Environment Troubleshooting": 42392, "Function Design &gt; Function Design Confirmation": 42411, "Function Design &gt; Function Design Creation": 42408, "Function Design &gt; Function Design Review": 42409, "Function Design &gt; Function Design Rework": 42410, "Management/Support &gt; Closure Activities": 42378, "Management/Support &gt; Deliverables": 42377, "Management/Support &gt; Progress Meeting": 42376, "Management/Support &gt; Project Monitoring": 42374, "Management/Support &gt; Project Planning": 42373, "Management/Support &gt; Translation Activities": 42375, "Project Support &gt; Support Activities": 42389, "Quality Management": 42417, "Requirements Analysis": 42418, "Test Specifications &gt; Test Specs Confirmation": 42416, "Test Specifications &gt; Test Specs Creation": 42413, "Test Specifications &gt; Test Specs Review": 42414, "Test Specifications &gt; Test Specs Rework": 42415, "Testing &gt; IT Bugfix": 42386, "Testing &gt; Integration Test": 42385, "Testing &gt; Local Test Code Execution": 42381, "Testing &gt; Pipeline Execution": 42382, "Testing &gt; Release Activities": 42387, "Testing &gt; Test Code Creation": 42380, "Testing &gt; UT Bugfix": 42384, "Testing &gt; UT Execution": 42383, "Training/Technical Turnover &gt; Study/Investigation": 42370, "Training/Technical Turnover &gt; Technical Turnover Meeting": 42371, "Triage Activities &gt; Issue Analysis and Management": 42402, "Triage Activities &gt; Quality Management": 42400, "Triage Activities &gt; Wrap-up Activities": 42401, "User Documentation &gt; User Documentation Creation": 42406, "User Documentation &gt; User Documentation Review": 42404, "User Documentation &gt; User Documentation Rework": 42405 }</t>
-  </si>
-  <si>
-    <t>INDIRECT_ACTIVITIES = { # Category 1: Project Management "Billing preparation": {"category": 1, "activity": 8}, "Create, Update Project Plan": {"category": 1, "activity": 2}, "Estimation": {"category": 1, "activity": 1}, "Progress meeting": {"category": 1, "activity": 7}, "Project initiation activities": {"category": 1, "activity": 3}, "Project monitoring activities": {"category": 1, "activity": 6}, "Project planning meetings": {"category": 1, "activity": 4}, "Review activities for planning": {"category": 1, "activity": 5}, # Category 2: Requirements Development "Analysis of requirements documents": {"category": 2, "activity": 12}, "Create, Update, Rework Requirements Documents": {"category": 2, "activity": 9}, "Prototyping": {"category": 2, "activity": 13}, "Review activities of requirements documents": {"category": 2, "activity": 10}, "Rework of requirements documents - MRs": {"category": 2, "activity": 11}, # Category 3: Basic Design "Create, Update, Rework BD documents": {"category": 3, "activity": 14}, "Review activities of BD documents": {"category": 3, "activity": 15}, "Rework of BD documents - MRs": {"category": 3, "activity": 16}, # Category 4: IT Specification "Create, Update, Rework IT Specifications": {"category": 4, "activity": 17}, "Review activities of IT specifications": {"category": 4, "activity": 18}, "Rework of IT specifications - MRs": {"category": 4, "activity": 19}, # Category 5: SIT Specification "Create, Update, Rework SIT specifications": {"category": 5, "activity": 20}, "Review activities of SIT specifications": {"category": 5, "activity": 21}, "Rework of SIT specifications - MRs": {"category": 5, "activity": 22}, # Category 6: DQA Specification "Create, Update, Rework DQA Specifications": {"category": 6, "activity": 23}, "Review activities of DQA specifications": {"category": 6, "activity": 24}, "Rework of DQA specifications - MRs": {"category": 6, "activity": 25}, # Category 7: Function Design "Create, Update, Rework FD documents": {"category": 7, "activity": 26}, "Review activities of FD documents": {"category": 7, "activity": 27}, "Rework of FD documents - MRs": {"category": 7, "activity": 28}, # Category 8: FT Specification "Create, Update, Rework FT specifications": {"category": 8, "activity": 29}, "Review activities of FT specifications": {"category": 8, "activity": 30}, "Rework of FT specifications - MRs": {"category": 8, "activity": 31}, # Category 9: Detailed Design "Create, Update, Rework DD documents": {"category": 9, "activity": 32}, "Review activities of DD documents": {"category": 9, "activity": 33}, "Rework of DD documents - MRs": {"category": 9, "activity": 34}, # Category 10: UT Specification "Create, Update, Rework UT specifications": {"category": 10, "activity": 35}, "Review activities of UT specifications": {"category": 10, "activity": 36}, "Rework of UT specifications - MRs": {"category": 10, "activity": 37}, # Category 11: Coding "Create, Update of Source Codes": {"category": 11, "activity": 38}, "Review activities of source codes": {"category": 11, "activity": 39}, "Rework of source code - MRs": {"category": 11, "activity": 40}, # Category 12: Test Code "Create, Update, Rework Test Code": {"category": 12, "activity": 41}, "Review activities of test code": {"category": 12, "activity": 42}, "Rework of test code - MRs": {"category": 12, "activity": 43}, # Category 13: Unit Testing "Bug fix of UT bugs": {"category": 13, "activity": 45}, "Bug investigation of UT bugs": {"category": 13, "activity": 44}, "Review, Confirmation of UT bug fixes": {"category": 13, "activity": 46}, # Category 14: Integration Testing "Bug fix of FT or IT bugs": {"category": 14, "activity": 48}, "Bug investigation of FT or IT bugs": {"category": 14, "activity": 47}, "Review or Confirmation of FT, IT bug fixes": {"category": 14, "activity": 49}, # Category 15: SI Testing "Bug fix of SIT bugs": {"category": 15, "activity": 51}, "Bug investigation of SIT bugs": {"category": 15, "activity": 50}, "Review or Confirmation of SIT bug fixes": {"category": 15, "activity": 52}, # Category 16: Delivery Quality Assurance "Bug fix of DQA bugs": {"category": 16, "activity": 54}, "Bug investigation of DQA bugs": {"category": 16, "activity": 53}, "Review or Confirmation of DQA bug fixes": {"category": 16, "activity": 55}, # Category 17: Field Bugs "Bug fix of field bugs": {"category": 17, "activity": 57}, "Bug investigation of field bugs": {"category": 17, "activity": 56}, "Review or Confirmation of field bug fixes": {"category": 17, "activity": 58}, # Category 18: Maintenance "Bug fix (Pure Maintenance or Commercial Support)": {"category": 18, "activity": 60}, "Bug investigation (Pure Maintenance or Commercial Support)": {"category": 18, "activity": 59}, "Review, Confirmation of bug fixes (Pure Maintenance, Commercial Support)": {"category": 18, "activity": 61}, # Category 19: Testing "DQA activities": {"category": 19, "activity": 65}, "Function or Integration Test Activities": {"category": 19, "activity": 63}, "Other testing (with specs)": {"category": 19, "activity": 66}, "Other testing (without specs)": {"category": 19, "activity": 67}, "System integration test activities": {"category": 19, "activity": 64}, "Unit test activities": {"category": 19, "activity": 62}, # Category 20: Quality Management "Quality management": {"category": 20, "activity": 68}, # Category 21: Wrap-up Activities "Wrap-up activities": {"category": 21, "activity": 69}, # Category 22: Configuration Management "CM administration activities": {"category": 22, "activity": 71}, "CM audit": {"category": 22, "activity": 72}, "CM environment preparation activities": {"category": 22, "activity": 70}, "Release activities": {"category": 22, "activity": 73}, # Category 23: User Documentation "Create, Update, Rework End-user Documentation": {"category": 23, "activity": 74}, "Review activities of end-user documentation": {"category": 23, "activity": 75}, "Rework of end-user documentation - MRs": {"category": 23, "activity": 76}, "Translation of end-user documentation.": {"category": 23, "activity": 77}, # Category 24: Support Activities "Technical support activities (active)": {"category": 24, "activity": 78}, "Technical support activities (standby)": {"category": 24, "activity": 79}, # Category 25: Vendor Inquiry "Request support from vendors": {"category": 25, "activity": 80}, # Category 26: Learning "Attendance activities (Cultural 1)": {"category": 26, "activity": 83}, "Attendance activities (Cultural 2)": {"category": 26, "activity": 97}, "Attendance activities (Cultural 3)": {"category": 26, "activity": 98}, "Attendance activities (Cultural 4)": {"category": 26, "activity": 99}, "Attendance activities (Cultural 5 - NIHONGO)": {"category": 26, "activity": 100}, "Attendance activities (Technical 1)": {"category": 26, "activity": 82}, "Attendance activities (Technical 2)": {"category": 26, "activity": 101}, "Attendance activities (Technical 3)": {"category": 26, "activity": 102}, "Attendance activities (Technical 4)": {"category": 26, "activity": 103}, "Attendance activities (Technical 5)": {"category": 26, "activity": 104}, "Research, Study activities, Technical Transfer": {"category": 26, "activity": 81}, # Category 27: Teaching "Teaching, Facilitation (Technical Transfer)": {"category": 27, "activity": 84}, "Teaching, Facilitation activities (Cultural)": {"category": 27, "activity": 86}, "Teaching, Facilitation activities (Technical)": {"category": 27, "activity": 85}, # Category 28: System Administration "Hardware management activities": {"category": 28, "activity": 87}, "Software system management activities": {"category": 28, "activity": 88}, # Category 29: Marketing "Marketing, Pre-Sales, Sales activities": {"category": 29, "activity": 89}, # Category 30: Systems Engineering "Systems Engineering": {"category": 30, "activity": 90}, # Category 31: Systems Integration "Systems Integration": {"category": 31, "activity": 91}, # Category 32: Others "Company or group activities": {"category": 32, "activity": 92}, "Managers meetings": {"category": 32, "activity": 93}, "Others": {"category": 32, "activity": 95}, "Translation": {"category": 32, "activity": 94} }</t>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Activity ID</t>
+  </si>
+  <si>
+    <t>Coding &gt; Test Framework Code Creation</t>
+  </si>
+  <si>
+    <t>Coding &gt; Test Framework Code Review</t>
+  </si>
+  <si>
+    <t>Coding &gt; [Tool] Source Code Creation</t>
+  </si>
+  <si>
+    <t>Coding &gt; [Tool] Source Code Modification</t>
+  </si>
+  <si>
+    <t>Coding &gt; [Tool] Source Code Review</t>
+  </si>
+  <si>
+    <t>Environment Configuration and Management &gt; Environment Setup</t>
+  </si>
+  <si>
+    <t>Environment Configuration and Management &gt; Environment Troubleshooting</t>
+  </si>
+  <si>
+    <t>Function Design &gt; Function Design Confirmation</t>
+  </si>
+  <si>
+    <t>Function Design &gt; Function Design Creation</t>
+  </si>
+  <si>
+    <t>Function Design &gt; Function Design Review</t>
+  </si>
+  <si>
+    <t>Function Design &gt; Function Design Rework</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Closure Activities</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Deliverables</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Progress Meeting</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Project Monitoring</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Project Planning</t>
+  </si>
+  <si>
+    <t>Management/Support &gt; Translation Activities</t>
+  </si>
+  <si>
+    <t>Project Support &gt; Support Activities</t>
+  </si>
+  <si>
+    <t>Quality Management</t>
+  </si>
+  <si>
+    <t>Requirements Analysis</t>
+  </si>
+  <si>
+    <t>Test Specifications &gt; Test Specs Confirmation</t>
+  </si>
+  <si>
+    <t>Test Specifications &gt; Test Specs Creation</t>
+  </si>
+  <si>
+    <t>Test Specifications &gt; Test Specs Review</t>
+  </si>
+  <si>
+    <t>Test Specifications &gt; Test Specs Rework</t>
+  </si>
+  <si>
+    <t>Testing &gt; IT Bugfix</t>
+  </si>
+  <si>
+    <t>Testing &gt; Integration Test</t>
+  </si>
+  <si>
+    <t>Testing &gt; Local Test Code Execution</t>
+  </si>
+  <si>
+    <t>Testing &gt; Pipeline Execution</t>
+  </si>
+  <si>
+    <t>Testing &gt; Release Activities</t>
+  </si>
+  <si>
+    <t>Testing &gt; Test Code Creation</t>
+  </si>
+  <si>
+    <t>Testing &gt; UT Bugfix</t>
+  </si>
+  <si>
+    <t>Testing &gt; UT Execution</t>
+  </si>
+  <si>
+    <t>Training/Technical Turnover &gt; Study/Investigation</t>
+  </si>
+  <si>
+    <t>Training/Technical Turnover &gt; Technical Turnover Meeting</t>
+  </si>
+  <si>
+    <t>Triage Activities &gt; Issue Analysis and Management</t>
+  </si>
+  <si>
+    <t>Triage Activities &gt; Quality Management</t>
+  </si>
+  <si>
+    <t>Triage Activities &gt; Wrap-up Activities</t>
+  </si>
+  <si>
+    <t>User Documentation &gt; User Documentation Creation</t>
+  </si>
+  <si>
+    <t>User Documentation &gt; User Documentation Review</t>
+  </si>
+  <si>
+    <t>User Documentation &gt; User Documentation Rework</t>
+  </si>
+  <si>
+    <t>Category Name</t>
+  </si>
+  <si>
+    <t>Category ID</t>
+  </si>
+  <si>
+    <t>Indirect</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Estimation</t>
+  </si>
+  <si>
+    <t>Create, Update Project Plan</t>
+  </si>
+  <si>
+    <t>Project initiation activities</t>
+  </si>
+  <si>
+    <t>Project planning meetings</t>
+  </si>
+  <si>
+    <t>Review activities for planning</t>
+  </si>
+  <si>
+    <t>Project monitoring activities</t>
+  </si>
+  <si>
+    <t>Progress meeting</t>
+  </si>
+  <si>
+    <t>Billing preparation</t>
+  </si>
+  <si>
+    <t>Requirements Development</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework Requirements Documents</t>
+  </si>
+  <si>
+    <t>Review activities of requirements documents</t>
+  </si>
+  <si>
+    <t>Rework of requirements documents - MRs</t>
+  </si>
+  <si>
+    <t>Analysis of requirements documents</t>
+  </si>
+  <si>
+    <t>Prototyping</t>
+  </si>
+  <si>
+    <t>Basic Design</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework BD documents</t>
+  </si>
+  <si>
+    <t>Review activities of BD documents</t>
+  </si>
+  <si>
+    <t>Rework of BD documents - MRs</t>
+  </si>
+  <si>
+    <t>IT Specification</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework IT Specifications</t>
+  </si>
+  <si>
+    <t>Review activities of IT specifications</t>
+  </si>
+  <si>
+    <t>Rework of IT specifications - MRs</t>
+  </si>
+  <si>
+    <t>SIT Specification</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework SIT specifications</t>
+  </si>
+  <si>
+    <t>Review activities of SIT specifications</t>
+  </si>
+  <si>
+    <t>Rework of SIT specifications - MRs</t>
+  </si>
+  <si>
+    <t>DQA Specification</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework DQA Specifications</t>
+  </si>
+  <si>
+    <t>Review activities of DQA specifications</t>
+  </si>
+  <si>
+    <t>Rework of DQA specifications - MRs</t>
+  </si>
+  <si>
+    <t>Function Design</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework FD documents</t>
+  </si>
+  <si>
+    <t>Review activities of FD documents</t>
+  </si>
+  <si>
+    <t>Rework of FD documents - MRs</t>
+  </si>
+  <si>
+    <t>FT Specification</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework FT specifications</t>
+  </si>
+  <si>
+    <t>Review activities of FT specifications</t>
+  </si>
+  <si>
+    <t>Rework of FT specifications - MRs</t>
+  </si>
+  <si>
+    <t>Detailed Design</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework DD documents</t>
+  </si>
+  <si>
+    <t>Review activities of DD documents</t>
+  </si>
+  <si>
+    <t>Rework of DD documents - MRs</t>
+  </si>
+  <si>
+    <t>UT Specification</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework UT specifications</t>
+  </si>
+  <si>
+    <t>Review activities of UT specifications</t>
+  </si>
+  <si>
+    <t>Rework of UT specifications - MRs</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>Create, Update of Source Codes</t>
+  </si>
+  <si>
+    <t>Review activities of source codes</t>
+  </si>
+  <si>
+    <t>Rework of source code - MRs</t>
+  </si>
+  <si>
+    <t>Test Code</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework Test Code</t>
+  </si>
+  <si>
+    <t>Review activities of test code</t>
+  </si>
+  <si>
+    <t>Rework of test code - MRs</t>
+  </si>
+  <si>
+    <t>Unit Testing</t>
+  </si>
+  <si>
+    <t>Bug investigation of UT bugs</t>
+  </si>
+  <si>
+    <t>Bug fix of UT bugs</t>
+  </si>
+  <si>
+    <t>Review, Confirmation of UT bug fixes</t>
+  </si>
+  <si>
+    <t>Integration Testing</t>
+  </si>
+  <si>
+    <t>Bug investigation of FT or IT bugs</t>
+  </si>
+  <si>
+    <t>Bug fix of FT or IT bugs</t>
+  </si>
+  <si>
+    <t>Review or Confirmation of FT, IT bug fixes</t>
+  </si>
+  <si>
+    <t>SI Testing</t>
+  </si>
+  <si>
+    <t>Bug investigation of SIT bugs</t>
+  </si>
+  <si>
+    <t>Bug fix of SIT bugs</t>
+  </si>
+  <si>
+    <t>Review or Confirmation of SIT bug fixes</t>
+  </si>
+  <si>
+    <t>Delivery Quality Assurance</t>
+  </si>
+  <si>
+    <t>Bug investigation of DQA bugs</t>
+  </si>
+  <si>
+    <t>Bug fix of DQA bugs</t>
+  </si>
+  <si>
+    <t>Review or Confirmation of DQA bug fixes</t>
+  </si>
+  <si>
+    <t>Field Bugs</t>
+  </si>
+  <si>
+    <t>Bug investigation of field bugs</t>
+  </si>
+  <si>
+    <t>Bug fix of field bugs</t>
+  </si>
+  <si>
+    <t>Review or Confirmation of field bug fixes</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Bug investigation (Pure Maintenance or Commercial Support)</t>
+  </si>
+  <si>
+    <t>Bug fix (Pure Maintenance or Commercial Support)</t>
+  </si>
+  <si>
+    <t>Review, Confirmation of bug fixes (Pure Maintenance, Commercial Support)</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Unit test activities</t>
+  </si>
+  <si>
+    <t>Function or Integration Test Activities</t>
+  </si>
+  <si>
+    <t>System integration test activities</t>
+  </si>
+  <si>
+    <t>DQA activities</t>
+  </si>
+  <si>
+    <t>Other testing (with specs)</t>
+  </si>
+  <si>
+    <t>Other testing (without specs)</t>
+  </si>
+  <si>
+    <t>Quality management</t>
+  </si>
+  <si>
+    <t>Wrap-up Activities</t>
+  </si>
+  <si>
+    <t>Wrap-up activities</t>
+  </si>
+  <si>
+    <t>Configuration Management</t>
+  </si>
+  <si>
+    <t>CM environment preparation activities</t>
+  </si>
+  <si>
+    <t>CM administration activities</t>
+  </si>
+  <si>
+    <t>CM audit</t>
+  </si>
+  <si>
+    <t>Release activities</t>
+  </si>
+  <si>
+    <t>User Documentation</t>
+  </si>
+  <si>
+    <t>Create, Update, Rework End-user Documentation</t>
+  </si>
+  <si>
+    <t>Review activities of end-user documentation</t>
+  </si>
+  <si>
+    <t>Rework of end-user documentation - MRs</t>
+  </si>
+  <si>
+    <t>Translation of end-user documentation.</t>
+  </si>
+  <si>
+    <t>Support Activities</t>
+  </si>
+  <si>
+    <t>Technical support activities (active)</t>
+  </si>
+  <si>
+    <t>Technical support activities (standby)</t>
+  </si>
+  <si>
+    <t>Vendor Inquiry</t>
+  </si>
+  <si>
+    <t>Request support from vendors</t>
+  </si>
+  <si>
+    <t>Learning</t>
+  </si>
+  <si>
+    <t>Research, Study activities, Technical Transfer</t>
+  </si>
+  <si>
+    <t>Attendance activities (Technical 1)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Cultural 1)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Cultural 2)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Cultural 3)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Cultural 4)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Cultural 5 - NIHONGO)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Technical 2)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Technical 3)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Technical 4)</t>
+  </si>
+  <si>
+    <t>Attendance activities (Technical 5)</t>
+  </si>
+  <si>
+    <t>Teaching</t>
+  </si>
+  <si>
+    <t>Teaching, Facilitation (Technical Transfer)</t>
+  </si>
+  <si>
+    <t>Teaching, Facilitation activities (Technical)</t>
+  </si>
+  <si>
+    <t>Teaching, Facilitation activities (Cultural)</t>
+  </si>
+  <si>
+    <t>System Administration</t>
+  </si>
+  <si>
+    <t>Hardware management activities</t>
+  </si>
+  <si>
+    <t>Software system management activities</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Marketing, Pre-Sales, Sales activities</t>
+  </si>
+  <si>
+    <t>Systems Engineering</t>
+  </si>
+  <si>
+    <t>Systems Integration</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Company or group activities</t>
+  </si>
+  <si>
+    <t>Managers meetings</t>
+  </si>
+  <si>
+    <t>Translation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +604,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -98,7 +633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -121,14 +656,239 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,13 +1224,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DADB6B1B-34F9-4768-84E0-6D679651B3CC}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -489,6 +1250,1133 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="17">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="17">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="17">
+        <v>3</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="17">
+        <v>2</v>
+      </c>
+      <c r="E5" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>46174</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1</v>
+      </c>
+      <c r="E6" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>46175</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="17">
+        <v>1</v>
+      </c>
+      <c r="E7" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>46175</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="17">
+        <v>1</v>
+      </c>
+      <c r="E8" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>46175</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="17">
+        <v>5</v>
+      </c>
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>46175</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="17">
+        <v>1</v>
+      </c>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>46176</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="17">
+        <v>1</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>46176</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="17">
+        <v>3</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>46176</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="17">
+        <v>3</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>46176</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="17">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>46177</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="17">
+        <v>1</v>
+      </c>
+      <c r="E15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>46177</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="17">
+        <v>3</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>46177</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="17">
+        <v>3</v>
+      </c>
+      <c r="E17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>46177</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D18" s="17">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>46178</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="17">
+        <v>1</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>46178</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="17">
+        <v>3</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>46178</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="17">
+        <v>3</v>
+      </c>
+      <c r="E21" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>46178</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="17">
+        <v>1</v>
+      </c>
+      <c r="E22" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="14"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="14"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="14"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="14"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="14"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="14"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="14"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="14"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="14"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="14"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="14"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="14"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="14"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="14"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="14"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="14"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="14"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="14"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="14"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="14"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="14"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="14"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="14"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="14"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="14"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="14"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="14"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="14"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="14"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="14"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="14"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="14"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="14"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="14"/>
+      <c r="B135" s="14"/>
+      <c r="C135" s="14"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="14"/>
+      <c r="B136" s="14"/>
+      <c r="C136" s="14"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="14"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="14"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="14"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="14"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="14"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="14"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="14"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="14"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="14"/>
+      <c r="B141" s="14"/>
+      <c r="C141" s="14"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="14"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="14"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="14"/>
+      <c r="B143" s="14"/>
+      <c r="C143" s="14"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="14"/>
+      <c r="B144" s="14"/>
+      <c r="C144" s="14"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="14"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="14"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="14"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="14"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="14"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="14"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="14"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="14"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="14"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="14"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="14"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="14"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="14"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="14"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="14"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="14"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="14"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="14"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="14"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="14"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="14"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="14"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="14"/>
+      <c r="B160" s="14"/>
+      <c r="C160" s="14"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="14"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="14"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="14"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="14"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="14"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="14"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="14"/>
+      <c r="B165" s="14"/>
+      <c r="C165" s="14"/>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="14"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="14"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="14"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="14"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="14"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="14"/>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="14"/>
+      <c r="B169" s="14"/>
+      <c r="C169" s="14"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="14"/>
+      <c r="B170" s="14"/>
+      <c r="C170" s="14"/>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="14"/>
+      <c r="B171" s="14"/>
+      <c r="C171" s="14"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="14"/>
+      <c r="B172" s="14"/>
+      <c r="C172" s="14"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="14"/>
+      <c r="B173" s="14"/>
+      <c r="C173" s="14"/>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="14"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="14"/>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="14"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="14"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="14"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -497,20 +2385,2159 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78566634-3844-4830-9F10-A85C5CCAE19B}">
-  <dimension ref="B2:B3"/>
+  <dimension ref="B1:K105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="60.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="55.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="1" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>6</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="10">
+        <v>42394</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="9">
+        <v>1</v>
+      </c>
+      <c r="K3" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4">
+        <v>42395</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4">
+        <v>42396</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4">
+        <v>42398</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4">
+        <v>42397</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4">
+        <v>42391</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="4">
+        <v>42392</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4">
+        <v>42411</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4">
+        <v>42408</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4">
+        <v>42409</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="2">
+        <v>2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4">
+        <v>42410</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="2">
+        <v>2</v>
+      </c>
+      <c r="K13" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="4">
+        <v>42378</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="2">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <v>42377</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="4">
+        <v>42376</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="2">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="4">
+        <v>42374</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="2">
+        <v>3</v>
+      </c>
+      <c r="K17" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="4">
+        <v>42373</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" s="2">
+        <v>3</v>
+      </c>
+      <c r="K18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="4">
+        <v>42375</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" s="2">
+        <v>4</v>
+      </c>
+      <c r="K19" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="4">
+        <v>42389</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J20" s="2">
+        <v>4</v>
+      </c>
+      <c r="K20" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="4">
+        <v>42417</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="2">
+        <v>4</v>
+      </c>
+      <c r="K21" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="4">
+        <v>42418</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5</v>
+      </c>
+      <c r="K22" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="4">
+        <v>42416</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="2">
+        <v>5</v>
+      </c>
+      <c r="K23" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4">
+        <v>42413</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="2">
+        <v>5</v>
+      </c>
+      <c r="K24" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="4">
+        <v>42414</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="2">
+        <v>6</v>
+      </c>
+      <c r="K25" s="4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="4">
+        <v>42415</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="2">
+        <v>6</v>
+      </c>
+      <c r="K26" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="4">
+        <v>42386</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="2">
+        <v>6</v>
+      </c>
+      <c r="K27" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="4">
+        <v>42385</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="2">
+        <v>7</v>
+      </c>
+      <c r="K28" s="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="4">
+        <v>42381</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="2">
+        <v>7</v>
+      </c>
+      <c r="K29" s="4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="4">
+        <v>42382</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J30" s="2">
+        <v>7</v>
+      </c>
+      <c r="K30" s="4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="4">
+        <v>42387</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="2">
+        <v>8</v>
+      </c>
+      <c r="K31" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="4">
+        <v>42380</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="2">
+        <v>8</v>
+      </c>
+      <c r="K32" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="4">
+        <v>42384</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J33" s="2">
+        <v>8</v>
+      </c>
+      <c r="K33" s="4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="4">
+        <v>42383</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" s="2">
+        <v>9</v>
+      </c>
+      <c r="K34" s="4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="4">
+        <v>42370</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" s="2">
+        <v>9</v>
+      </c>
+      <c r="K35" s="4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="4">
+        <v>42371</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J36" s="2">
+        <v>9</v>
+      </c>
+      <c r="K36" s="4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="4">
+        <v>42402</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" s="2">
+        <v>10</v>
+      </c>
+      <c r="K37" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="4">
+        <v>42400</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J38" s="2">
+        <v>10</v>
+      </c>
+      <c r="K38" s="4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="4">
+        <v>42401</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J39" s="2">
+        <v>10</v>
+      </c>
+      <c r="K39" s="4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="4">
+        <v>42406</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J40" s="2">
+        <v>11</v>
+      </c>
+      <c r="K40" s="4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="4">
+        <v>42404</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J41" s="2">
+        <v>11</v>
+      </c>
+      <c r="K41" s="4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="7">
+        <v>42405</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J42" s="2">
+        <v>11</v>
+      </c>
+      <c r="K42" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J43" s="2">
+        <v>12</v>
+      </c>
+      <c r="K43" s="4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J44" s="2">
+        <v>12</v>
+      </c>
+      <c r="K44" s="4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="2">
+        <v>12</v>
+      </c>
+      <c r="K45" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="2">
+        <v>13</v>
+      </c>
+      <c r="K46" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G47" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J47" s="2">
+        <v>13</v>
+      </c>
+      <c r="K47" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48" s="2">
+        <v>13</v>
+      </c>
+      <c r="K48" s="4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G49" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J49" s="2">
+        <v>14</v>
+      </c>
+      <c r="K49" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J50" s="2">
+        <v>14</v>
+      </c>
+      <c r="K50" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G51" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J51" s="2">
+        <v>14</v>
+      </c>
+      <c r="K51" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G52" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J52" s="2">
+        <v>15</v>
+      </c>
+      <c r="K52" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J53" s="2">
+        <v>15</v>
+      </c>
+      <c r="K53" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G54" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J54" s="2">
+        <v>15</v>
+      </c>
+      <c r="K54" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G55" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55" s="2">
+        <v>16</v>
+      </c>
+      <c r="K55" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J56" s="2">
+        <v>16</v>
+      </c>
+      <c r="K56" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G57" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J57" s="2">
+        <v>16</v>
+      </c>
+      <c r="K57" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G58" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J58" s="2">
+        <v>17</v>
+      </c>
+      <c r="K58" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G59" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J59" s="2">
+        <v>17</v>
+      </c>
+      <c r="K59" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G60" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J60" s="2">
+        <v>17</v>
+      </c>
+      <c r="K60" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="7:11" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G61" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J61" s="2">
+        <v>18</v>
+      </c>
+      <c r="K61" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J62" s="2">
+        <v>18</v>
+      </c>
+      <c r="K62" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="7:11" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G63" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J63" s="2">
+        <v>18</v>
+      </c>
+      <c r="K63" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G64" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J64" s="2">
+        <v>19</v>
+      </c>
+      <c r="K64" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G65" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J65" s="2">
+        <v>19</v>
+      </c>
+      <c r="K65" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G66" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J66" s="2">
+        <v>19</v>
+      </c>
+      <c r="K66" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J67" s="2">
+        <v>19</v>
+      </c>
+      <c r="K67" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G68" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J68" s="2">
+        <v>19</v>
+      </c>
+      <c r="K68" s="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J69" s="2">
+        <v>19</v>
+      </c>
+      <c r="K69" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G70" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J70" s="2">
+        <v>20</v>
+      </c>
+      <c r="K70" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G71" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J71" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" s="4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G72" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J72" s="2">
+        <v>22</v>
+      </c>
+      <c r="K72" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G73" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J73" s="2">
+        <v>22</v>
+      </c>
+      <c r="K73" s="4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G74" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="J74" s="2">
+        <v>22</v>
+      </c>
+      <c r="K74" s="4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J75" s="2">
+        <v>22</v>
+      </c>
+      <c r="K75" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G76" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J76" s="2">
+        <v>23</v>
+      </c>
+      <c r="K76" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J77" s="2">
+        <v>23</v>
+      </c>
+      <c r="K77" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G78" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J78" s="2">
+        <v>23</v>
+      </c>
+      <c r="K78" s="4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G79" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J79" s="2">
+        <v>23</v>
+      </c>
+      <c r="K79" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J80" s="2">
+        <v>24</v>
+      </c>
+      <c r="K80" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G81" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J81" s="2">
+        <v>24</v>
+      </c>
+      <c r="K81" s="4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G82" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J82" s="2">
+        <v>25</v>
+      </c>
+      <c r="K82" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J83" s="2">
+        <v>26</v>
+      </c>
+      <c r="K83" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J84" s="2">
+        <v>26</v>
+      </c>
+      <c r="K84" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J85" s="2">
+        <v>26</v>
+      </c>
+      <c r="K85" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J86" s="2">
+        <v>26</v>
+      </c>
+      <c r="K86" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J87" s="2">
+        <v>26</v>
+      </c>
+      <c r="K87" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G88" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J88" s="2">
+        <v>26</v>
+      </c>
+      <c r="K88" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="89" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G89" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J89" s="2">
+        <v>26</v>
+      </c>
+      <c r="K89" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G90" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J90" s="2">
+        <v>26</v>
+      </c>
+      <c r="K90" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="91" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G91" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J91" s="2">
+        <v>26</v>
+      </c>
+      <c r="K91" s="4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="92" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G92" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J92" s="2">
+        <v>26</v>
+      </c>
+      <c r="K92" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J93" s="2">
+        <v>26</v>
+      </c>
+      <c r="K93" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G94" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J94" s="2">
+        <v>27</v>
+      </c>
+      <c r="K94" s="4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="95" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G95" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="J95" s="2">
+        <v>27</v>
+      </c>
+      <c r="K95" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G96" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J96" s="2">
+        <v>27</v>
+      </c>
+      <c r="K96" s="4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="97" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G97" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J97" s="2">
+        <v>28</v>
+      </c>
+      <c r="K97" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="98" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G98" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J98" s="2">
+        <v>28</v>
+      </c>
+      <c r="K98" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="99" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G99" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J99" s="2">
+        <v>29</v>
+      </c>
+      <c r="K99" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J100" s="2">
+        <v>30</v>
+      </c>
+      <c r="K100" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G101" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J101" s="2">
+        <v>31</v>
+      </c>
+      <c r="K101" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G102" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J102" s="2">
+        <v>32</v>
+      </c>
+      <c r="K102" s="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G103" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="J103" s="2">
+        <v>32</v>
+      </c>
+      <c r="K103" s="4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G104" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J104" s="2">
+        <v>32</v>
+      </c>
+      <c r="K104" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="105" spans="7:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G105" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="J105" s="6">
+        <v>32</v>
+      </c>
+      <c r="K105" s="7">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>